--- a/Result/checksun_type/穿戴式裝置.xlsx
+++ b/Result/checksun_type/穿戴式裝置.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>17.53</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>18.24</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>18.83</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>18.83</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>275.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>134</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>113.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>150.4</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>150.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>5.094059701290561</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>275</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>275.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>17.7</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>18.87</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>18.87</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>19.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>93.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>93.40000000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>88.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>152.68</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>152.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9.995558126169087</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>19</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>17.61</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>18.37</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>18.9</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>18.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>128.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>128.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>97.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>152.7</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>152.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-3.766599375176838</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>18</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>17.77</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>18.43</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>18.93</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>18.93</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>231.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>129.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>129.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>109.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>153.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>153.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>5.373577389639848</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>231</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>17.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>18.52</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>18.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>127.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>112.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>104.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>149.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-4.582369281680613</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>127</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>18.31</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>18.64</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>18.99</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>92.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>97.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>147.2</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>147.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-7.498637052078394</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>72</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>18.51</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>18.74</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>19.01</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>196.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>83.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>83.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>97.4</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>147.56</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>147.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-5.504068257929575</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>196</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,21 +4067,17 @@
           <t>18.81</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AM9" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>19.04</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
       <c r="AP9" t="inlineStr">
         <is>
           <t>12.53</t>
@@ -4164,20 +4118,16 @@
           <t>22.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>98.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>145.88</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>145.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-15.74382468564805</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>22</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,21 +4497,17 @@
           <t>18.83</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>18.92</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AM10" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>19.04</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
       <c r="AP10" t="inlineStr">
         <is>
           <t>21.95</t>
@@ -4600,20 +4548,16 @@
           <t>146.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>89.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>105.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>149.38</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>149.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-11.1669115579013</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>146</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>18.78</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>19.03</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>96.59999999999999</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>109.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>148.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>148.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-17.51536024833804</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>26</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>18.66</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>19.03</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>103.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>103.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>112.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>149.84</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>149.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-13.10188122580702</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>26</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>12.44</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>13.8</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>13.8</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>726101414.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>522491393.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>522491393.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>500252244.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>951906310.08</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>951906310.08</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-27507192.40119457</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>726101414</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>726101414.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>12.32</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>13.81</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>13.81</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>298259044.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>458588598.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>458588598.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>469412312.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>952356783.44</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>952356783.4400001</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-51416436.28370804</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>298259044</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>298259044.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>12.31</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>13.16</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>13.83</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>13.83</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>653442603.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>539127122.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>539127122.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>523171176.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>958838697.5</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>958838697.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-37895943.748595</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>653442603</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>653442603.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>12.44</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>13.24</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>13.86</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>13.86</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>528064397.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>496768343.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>496768343.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>529229061.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>954039194.6</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>954039194.6</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-55282909.17169785</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>528064397</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>528064397.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>12.61</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>13.34</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>13.9</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>406589511.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>475101346.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>475101346.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>526608726.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>957961469.06</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>957961469.0599999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-64713662.3771413</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>406589511</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>406589511.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>12.78</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>13.42</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>13.92</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>406587436.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>478013094.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>478013094.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>540193718.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>959510743.76</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>959510743.76</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-62859798.37144822</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>406587436</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>406587436.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>12.96</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>13.49</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>13.94</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>13.94</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>700951664.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>480236027.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>480236027.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>574567755.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>962186777.6</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>962186777.6</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-57966206.10004926</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>700951664</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>700951664.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>13.07</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>13.59</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>13.96</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>13.96</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>441648708.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>507215229.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>507215229.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>561036827.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>968670779.14</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>968670779.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-80444162.78019172</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>441648708</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>441648708.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>13.15</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>13.66</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>13.98</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>419729414.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>561689780.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>561689780.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>586608470.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>987821058.9</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>987821058.9</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-81900064.08110285</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>419729414</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>419729414.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>13.33</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>13.74</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>14</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>421148252.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>578116107.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>578116107</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>611710207.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>997706755.02</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>997706755.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-78706425.00807929</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>421148252</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>421148252.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>13.46</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>13.81</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>14.01</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>417702098.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>602374341.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>602374341.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>623134652.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1016363202.4</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1016363202.4</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-71485158.08204281</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>417702098</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>417702098.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>48.32</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>49.46</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>55.04</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>55.04</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>289324693.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>359053739.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>359053739.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>779219302.6</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1233289107.3</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1233289107.3</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-90860825.19125909</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>289324693</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>289324693.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>48.31</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>49.57</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>55.39</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>55.39</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>298587633.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>427404646.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>427404646.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>788465115.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1336844077.5</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1336844077.5</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-80434512.81531477</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>298587633</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>298587633.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>48.41</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>49.77</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>55.78</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>55.78</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>302147334.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>549695262.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>549695262.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>789932410.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1388106125.2</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1388106125.2</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-63659577.53484738</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>302147334</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>302147334.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>49.14</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>56.17</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>56.17</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>429086972.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>664802561.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>664802561.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>805598718.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1482928219.1</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1482928219.1</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-37803224.47222078</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>429086972</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>429086972.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>49.73999999999999</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>50.18</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>56.62</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>476122067.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>751503060.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>751503060.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>853426202.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1565117969.24</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1565117969.24</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-13116137.5801748</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>476122067</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>476122067.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>50.16</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>50.38</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>57.1</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>631079227.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1199384865.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1199384865.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>852262787.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1647059956.98</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1647059956.98</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>17580088.42918277</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>631079227</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>631079227.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>50.69</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>50.56</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>57.56</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>910040711.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>1149525583.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>1149525583.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>840320195.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1776903570.96</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1776903570.96</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>44201426.71293712</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>910040711</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>910040711.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>50.32</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>50.72</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>58.07</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>58.07</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>877683832.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1030169557.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1030169557.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>806899222.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1957468999.34</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1957468999.34</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>50764557.16426682</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>877683832</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>877683832.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>49.52</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>50.73</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>862589466.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>946394875.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>946394875.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>771003853.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2163437979.1</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2163437979.1</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>61794246.37458563</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>862589466</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>862589466.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>48.86</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>50.84</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>58.9</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>2715531091.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>955349345.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>955349345.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>721647627.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2402549153.18</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2402549153.18</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>76961261.37594843</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>2715531091</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>2715531091.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>48.84</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>50.98</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>59.29</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>59.29</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>381782819.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>505140710.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>505140710.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>501963719.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>2548936714.28</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2548936714.28</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-102649650.6355312</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>381782819</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>381782819.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>38.15</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>46.38</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>46.38</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>69926901.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>72419946.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>72419946.59999999</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-11311984.56733361</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>69926901</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>69926901.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>37.78</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>44.19</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>46.53</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>44.19</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>46.53</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>51098096.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>97760133.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>97760133.59999999</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>0</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-8847970.725226209</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>51098096</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>51098096.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>37.89</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>44.79</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>46.74</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>46.74</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>51016187.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>136033064.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>136033064.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>0</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-2994580.032028973</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>51016187</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>51016187.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>38.39</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>45.44</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>46.96</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>46.96</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>92544726.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>218971148.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>218971148.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>0</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>5483131.923682392</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>92544726</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>92544726.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>39.17</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>46.09</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>47.16</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>47.16</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>97513823.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>223966399.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>223966399.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>0</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>12948836.54170999</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>97513823</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>97513823.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>40.73999999999999</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>47.36</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>196627836.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>0</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>0</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>22619267.15525979</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>196627836</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>196627836.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>42.42</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>47.33</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>47.57</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>47.57</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>242462750.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>0</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>0</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>25006978.52621445</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>242462750</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>242462750.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>43.82</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>47.83</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>47.73</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>47.83</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>47.73</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>465706606.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>0</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>0</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>22614004.75164205</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>465706606</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>465706606.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>45.19</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>48.21</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>47.86</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>47.86</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>117520982.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>0</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>0</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-5531156.810305715</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>117520982</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>117520982.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>46.33</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>48.58</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>47.96</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>47.96</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>0</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>0</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-9100221.252076194</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>0</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>46.81</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>48.67</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>48</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>73812718.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>82573246.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>82573246.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>86844569.5</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>110626528.9</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>110626528.9</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-9100221.252076194</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>73812718</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>73812718.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>274.1</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>284.0</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>287.55</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>284</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>287.55</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>2688136980.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>3263432978.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>3263432978.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>4223412861.7</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>6255669421.98</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>6255669421.98</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-445450678.2614727</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>2688136980</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>2688136980.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>271.6</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>285.42</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>287.36</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>285.42</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>287.36</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>2621988947.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>3519578155.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>3519578155.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>4417765870.1</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>6360127659.86</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>6360127659.86</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-402188400.3754621</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>2621988947</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>2621988947.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>270.6</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>286.88</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>287.32</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>286.88</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>287.32</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>4268693515.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>4031559654.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>4031559654</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>4514008297.8</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>6506528606.38</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>6506528606.38</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-318933985.5606084</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>4268693515</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>4268693515.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>271.4</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>288.75</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>287.13</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>288.75</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>287.13</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>3893703258.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>3936434056.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>3936434056</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>4366545268.6</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>6525717328.16</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>6525717328.16</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-365041240.0550823</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>3893703258</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>3893703258.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>273.3</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>289.92</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>286.93</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>289.92</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>286.93</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>2844642193.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>4290924489.8</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>4290924489.8</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>4264472077.2</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>6529654870.68</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>6529654870.68</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-377694031.7952194</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>2844642193</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>2844642193.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>275.5</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>290.7</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>286.62</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>286.62</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>3968862865.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>5183392744.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>5183392744.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>4421198531.4</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>6513451334.96</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>6513451334.96</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-269880976.1813021</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>3968862865</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>3968862865.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>279.7</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>291.9</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>286.42</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>291.9</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>286.42</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>5181896439.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>5315953584.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>5315953584.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>4574167556.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>6486662651.14</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>6486662651.14</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-226675933.8692303</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>5181896439</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>5181896439.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>284.0</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>293.23</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>286.09</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>293.23</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>286.09</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>3793065525.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>4996456941.6</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>4996456941.6</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>4657174753.1</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>6458408539.78</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>6458408539.78</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-286826758.7137976</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>3793065525</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>3793065525.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>287.1</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>293.85</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>285.64</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>293.85</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>285.64</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>5666155427.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>4796656481.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>4796656481.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>4637753668.6</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>6465330044.68</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>6465330044.68</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-213709383.466258</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>5666155427</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>5666155427.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>288.6</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>294.45</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>285.17</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>294.45</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>285.17</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>7306983468.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>4238019664.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>4238019664.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>4486128549.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>6452821540.82</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>6452821540.82</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-302311716.0602636</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>7306983468</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>7306983468.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>290.2</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>294.5</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>284.72</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>284.72</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>4631667064.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>3659004318.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>3659004318</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>4399551051.9</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>6379548221.5</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>6379548221.5</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-593892634.2995472</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>4631667064</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>4631667064.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>586.6</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>636.0</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>667.3</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>636</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>667.3</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>2251806679.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>2845492684.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>2845492684.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>3254023064.0</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>2250939639.92</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>2250939639.92</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>80988449.20909452</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>2251806679</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>2251806679.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>577.4</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>640.85</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>668.88</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>640.85</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>668.88</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>2303990317.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>2895931468.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>2895931468.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>3423927956.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>2313304958.2</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>2313304958.2</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>168000892.6023631</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>2303990317</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>2303990317.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>572.0</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>646.8</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>670.44</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>670.4400000000001</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>4282414081.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>3701315712.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>3701315712</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>3406103963.5</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>2315429027.54</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>2315429027.54</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>280713247.2140913</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>4282414081</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>4282414081.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>653.25</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>671.96</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>671.96</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>3277325446.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>3639148367.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>3639148367.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>3149911827.2</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>2279747515.3</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>2279747515.3</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>219731448.8303423</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>3277325446</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>3277325446.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>589.0</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>659.5</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>673.4</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>673.4</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>2111926901.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>3434438489.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>3434438489.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>3061336173.2</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>2234436035.54</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>2234436035.54</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>232455110.2881894</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>2111926901</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>601.0</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>674.84</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>2504000596.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>3662553443.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>3053660242.7</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>2215412102.28</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>367193931.1105347</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>2504000596</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>2504000596.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>617.2</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>672.05</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>676.22</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>672.05</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>676.22</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>6330911536.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>3951924444.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>3951924444.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>3034497195.4</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>2193079344.64</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>2193079344.64</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>504555995.9956522</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>6330911536</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>6330911536.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>636.8</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>678.2</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>677.46</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>678.2</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>677.46</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>3971577357.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>3110892215.0</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>3110892215</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>2577610128.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2089597881.18</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2089597881.18</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>272741488.1174035</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>3971577357</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>3971577357.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>647.4</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>681.95</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>677.64</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>681.95</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>677.64</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>2253776059.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>2660675287.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>2660675287.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>2395309044.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2031062259.28</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2031062259.28</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>184622942.8942842</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>2253776059</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>2253776059.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>653.6</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>684.55</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>677.36</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>684.55</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>677.36</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>3252501668.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>2688233856.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>2688233856.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>2353124375.3</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2012331643.46</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2012331643.46</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>236195769.4007463</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>3252501668</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>3252501668.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>663.2</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>687.1</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>677.34</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>687.1</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>677.34</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>3950855603.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>2444767042.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>2444767042.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>2195634921.6</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>1973519631.2</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>1973519631.2</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>194429357.3956661</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>3950855603</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>3950855603.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>29.16</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>30.76</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>31.83</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>719006309.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>949851822.4</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>949851822.4</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>1034336783.1</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>1943240864.16</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>1943240864.16</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-130458949.546433</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>719006309</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>719006309.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>29.14</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>31.02</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>31.8</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>667847761.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>1067800185.6</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>1067800185.6</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>1021273105.5</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>1938830373.0</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>1938830373</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-121533602.5249245</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>667847761</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>667847761.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>31.26</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>31.77</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>31.77</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>1201959271.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>1180457053.0</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>1180457053</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>1068520962.5</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>1938375533.6</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>1938375533.6</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-98961347.97545075</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>1201959271</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>1201959271.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>29.03</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>31.59</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>31.76</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>31.76</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1119253658.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>1129061877.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>1129061877.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>1010725999.7</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>1921840103.86</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>1921840103.86</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-120407169.4056509</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1119253658</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1119253658.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>29.27999999999999</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>31.75</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>1041192113.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>1105345654.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>1105345654</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>978154218.3</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>1906340616.66</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>1906340616.66</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-137882485.4343059</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>1041192113</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>1041192113.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>29.53</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>32.23</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>31.72</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>31.72</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>1308748125.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>1118821743.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>1118821743.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>936141852.9</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>1892720250.14</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>1892720250.14</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-149559111.1740165</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>1308748125</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>1308748125.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>29.82</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>32.48</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>31.69</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>31.69</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>1231132098.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>974746025.4</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>974746025.4</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>901408156.9</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>1876762391.38</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>1876762391.38</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-189565323.8316743</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>1231132098</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>1231132098.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>30.22</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>32.69</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>31.66</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>944983395.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>956584872.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>956584872</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>919270819.4</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>1860013080.08</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>1860013080.08</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-231630863.170054</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>944983395</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>944983395.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>30.72</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>31.62</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>31.62</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>1000672539.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>892390121.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>892390121.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>905448004.3</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>1847387257.46</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>1847387257.46</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-252793170.361666</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>1000672539</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>1000672539.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>31.07</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>31.56</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>33</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>31.56</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>1108572562.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>850962782.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>850962782.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>944921985.7</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>1839319197.86</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>1839319197.86</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-279963404.2653377</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>1108572562</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>1108572562.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>31.44</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>31.5</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>588369533.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>753461962.0</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>753461962</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>1014121978.2</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>1826207989.06</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>1826207989.06</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-320340047.8682499</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>588369533</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>588369533.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
